--- a/data_pipeline/expense_assumption.xlsx
+++ b/data_pipeline/expense_assumption.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\internship\airflow\dbt_project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\internship\airflow\dbt_project\data_pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C7BF6C-916C-4EC4-A1F9-076EF7885262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C590F20-A20B-4779-82E6-00AE03D8A87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3C39F575-3141-44CB-B3DD-A98984FB79E5}"/>
   </bookViews>

--- a/data_pipeline/expense_assumption.xlsx
+++ b/data_pipeline/expense_assumption.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\internship\airflow\dbt_project\data_pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C590F20-A20B-4779-82E6-00AE03D8A87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF40317-C752-4116-94BA-FB61DC2A79DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3C39F575-3141-44CB-B3DD-A98984FB79E5}"/>
   </bookViews>
